--- a/artfynd/A 18266-2024 artfynd.xlsx
+++ b/artfynd/A 18266-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117590507</v>
+        <v>117590005</v>
       </c>
       <c r="B2" t="n">
-        <v>8416</v>
+        <v>78216</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574066</v>
+        <v>573975</v>
       </c>
       <c r="R2" t="n">
-        <v>6515763</v>
+        <v>6515745</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117590005</v>
+        <v>117590507</v>
       </c>
       <c r="B3" t="n">
-        <v>78216</v>
+        <v>8416</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573975</v>
+        <v>574066</v>
       </c>
       <c r="R3" t="n">
-        <v>6515745</v>
+        <v>6515763</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>

--- a/artfynd/A 18266-2024 artfynd.xlsx
+++ b/artfynd/A 18266-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117590005</v>
       </c>
       <c r="B2" t="n">
-        <v>78216</v>
+        <v>78218</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117590507</v>
+        <v>117589905</v>
       </c>
       <c r="B3" t="n">
-        <v>8416</v>
+        <v>78219</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574066</v>
+        <v>573975</v>
       </c>
       <c r="R3" t="n">
-        <v>6515763</v>
+        <v>6515745</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117589905</v>
+        <v>117590507</v>
       </c>
       <c r="B4" t="n">
-        <v>78217</v>
+        <v>8416</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573975</v>
+        <v>574066</v>
       </c>
       <c r="R4" t="n">
-        <v>6515745</v>
+        <v>6515763</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
